--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484790_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484790_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0947</v>
+        <v>3.7654</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1619</v>
+        <v>6.5224</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0672</v>
+        <v>-2.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2679</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3122</v>
+        <v>1.1426</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5801</v>
+        <v>-0.2017</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6649</v>
+        <v>5.5497</v>
       </c>
       <c r="K2" t="n">
-        <v>1.76</v>
+        <v>2.9159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9049</v>
+        <v>2.6338</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.9328</v>
+        <v>-4.6088</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4478</v>
+        <v>-1.7733</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.485</v>
+        <v>-2.8354</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0757</v>
+        <v>-1.1322</v>
       </c>
       <c r="R2" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2495</v>
+        <v>1.2019</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7239</v>
+        <v>0.8597</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5256</v>
+        <v>0.3422</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8488</v>
+        <v>1.2452</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2309</v>
+        <v>1.5155</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0407</v>
+        <v>1.763</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8099</v>
+        <v>-0.2475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1426</v>
+        <v>-0.3389</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2017</v>
+        <v>1.2991</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5497</v>
+        <v>1.5574</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9159</v>
+        <v>0.7348</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6338</v>
+        <v>0.8226</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.6088</v>
+        <v>-0.5972</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7733</v>
+        <v>-1.0737</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.8354</v>
+        <v>0.4765</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3327</v>
+        <v>0.0457</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.622</v>
+        <v>0.2056</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2893</v>
+        <v>-0.1598</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>0.3208</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7813</v>
+        <v>0.7218</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0553</v>
+        <v>1.2879</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.274</v>
+        <v>-0.5661</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.4657</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3389</v>
+        <v>-0.727</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2991</v>
+        <v>1.1928</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5574</v>
+        <v>1.3869</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7348</v>
+        <v>0.0211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8226</v>
+        <v>1.3658</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5972</v>
+        <v>-0.9212</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0737</v>
+        <v>-0.7482</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4765</v>
+        <v>-0.173</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3116</v>
+        <v>-0.3101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4979</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1863</v>
+        <v>-0.211</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>M. TAEÑO ELEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2411</v>
+        <v>0.6339</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9121</v>
+        <v>0.6339</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.671</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5812</v>
+        <v>0.6339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1847</v>
+        <v>0.6339</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7659</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4717</v>
+        <v>0.6339</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2507</v>
+        <v>0.6339</v>
       </c>
       <c r="L5" t="n">
-        <v>2.221</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.0529</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.066</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9869</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9627</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5582</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1578</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4004</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TAEÑO ELEZ</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,31 +877,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6339</v>
+        <v>0.617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6339</v>
+        <v>0.617</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6339</v>
+        <v>0.617</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6339</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6339</v>
+        <v>0.617</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6339</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.617</v>
+        <v>0.4313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.617</v>
+        <v>4.2921</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-3.8609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.617</v>
+        <v>-2.2679</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.3122</v>
       </c>
       <c r="I7" t="n">
-        <v>0.617</v>
+        <v>-2.5801</v>
       </c>
       <c r="J7" t="n">
-        <v>0.617</v>
+        <v>2.6649</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="L7" t="n">
-        <v>0.617</v>
+        <v>0.9049</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-4.9328</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.4478</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-3.485</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5861</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.8541</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.7319</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4946</v>
+        <v>0.0392</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0342</v>
+        <v>1.1081</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5397</v>
+        <v>-1.0689</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4657</v>
+        <v>-1.2647</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.727</v>
+        <v>0.3655</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1928</v>
+        <v>-1.6302</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3869</v>
+        <v>0.2134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0211</v>
+        <v>0.7396</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3658</v>
+        <v>-0.5262</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9212</v>
+        <v>-1.4781</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7482</v>
+        <v>-0.3741</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.173</v>
+        <v>-1.104</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5373</v>
+        <v>0.3039</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3527</v>
+        <v>0.2722</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1846</v>
+        <v>0.0318</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2711</v>
+        <v>0.0269</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7184</v>
+        <v>3.7243</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9895</v>
+        <v>-3.6974</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2647</v>
+        <v>-0.5812</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3655</v>
+        <v>0.1847</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6302</v>
+        <v>-0.7659</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2134</v>
+        <v>4.4717</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7396</v>
+        <v>2.2507</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5262</v>
+        <v>2.221</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4781</v>
+        <v>-5.0529</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3741</v>
+        <v>-2.066</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.104</v>
+        <v>-2.9869</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.9627</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0065</v>
+        <v>2.344</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1176</v>
+        <v>1.9701</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1111</v>
+        <v>0.374</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6226</v>
+        <v>0.3398</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6226</v>
+        <v>1.2452</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. CAMBRA NADAL</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2452</v>
+        <v>-0.4881</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2452</v>
+        <v>-1.2487</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.5471</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.5384</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.0087</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4.2724</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2.1819</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.0906</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-2.7253</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.6434</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-1.0819</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.9062</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.3048</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.4699</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.1651</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2452</v>
+        <v>1.2452</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>V. CAMBRA NADAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0562</v>
+        <v>-1.2452</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3313</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7249</v>
+        <v>-1.2452</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5471</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5384</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0087</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2724</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1819</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.0906</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7253</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6434</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0819</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.5853</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9062</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2633</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.622</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6413</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2452</v>
+        <v>-1.2452</v>
       </c>
       <c r="W11" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3208</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="12">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5532</v>
+        <v>-2.4903</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6783</v>
+        <v>2.1856</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2315</v>
+        <v>-4.6759</v>
       </c>
       <c r="G13" t="n">
         <v>-5.1817</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1381</v>
+        <v>1.201</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5008</v>
+        <v>1.0081</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3627</v>
+        <v>0.1929</v>
       </c>
       <c r="V13" t="n">
         <v>1.8678</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.6519</v>
+        <v>-4.3298</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8936</v>
+        <v>-3.3863</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7583</v>
+        <v>-0.9434</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6172</v>
@@ -1546,13 +1546,13 @@
         <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7512</v>
+        <v>-0.4291</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5291</v>
+        <v>-0.0218</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2222</v>
+        <v>-0.4073</v>
       </c>
       <c r="V14" t="n">
         <v>1.547</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.934700000000003</v>
+        <v>-3.053</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2102</v>
+        <v>18.0919</v>
       </c>
       <c r="F15" t="n">
-        <v>-21.1451</v>
+        <v>-21.1449</v>
       </c>
       <c r="G15" t="n">
         <v>-8.880800000000001</v>
@@ -1624,13 +1624,13 @@
         <v>10.3785</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2488</v>
+        <v>7.130599999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>5.5194</v>
+        <v>6.401199999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7293000000000005</v>
+        <v>0.7296</v>
       </c>
       <c r="V15" t="n">
         <v>6.245</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4658</v>
+        <v>8.0014</v>
       </c>
       <c r="E16" t="n">
-        <v>8.0824</v>
+        <v>8.8627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6166</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8218</v>
+        <v>7.8729</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4431</v>
+        <v>6.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3787</v>
+        <v>1.7992</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9584</v>
+        <v>9.4976</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4763</v>
+        <v>6.0753</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4821</v>
+        <v>3.4223</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1366</v>
+        <v>-1.6247</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0332</v>
+        <v>-0.0015</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1035</v>
+        <v>-1.6231</v>
       </c>
       <c r="P16" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8305</v>
+        <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9458</v>
+        <v>-0.3056</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5771</v>
+        <v>0.0259</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6313</v>
+        <v>-0.3315</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8112</v>
+        <v>-0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4904</v>
+        <v>1.2262</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3208</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.6627</v>
+        <v>6.2028</v>
       </c>
       <c r="E17" t="n">
-        <v>8.1807</v>
+        <v>6.7183</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.518</v>
+        <v>-0.5155</v>
       </c>
       <c r="G17" t="n">
-        <v>7.8729</v>
+        <v>1.8218</v>
       </c>
       <c r="H17" t="n">
-        <v>6.0737</v>
+        <v>1.4431</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7992</v>
+        <v>0.3787</v>
       </c>
       <c r="J17" t="n">
-        <v>9.4976</v>
+        <v>4.9584</v>
       </c>
       <c r="K17" t="n">
-        <v>6.0753</v>
+        <v>3.4763</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4223</v>
+        <v>1.4821</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6247</v>
+        <v>-3.1366</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0015</v>
+        <v>-2.0332</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6231</v>
+        <v>-1.1035</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6418</v>
+        <v>2.8305</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6442</v>
+        <v>-0.3172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6561</v>
+        <v>0.213</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9881</v>
+        <v>-0.5302</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3208</v>
+        <v>2.8112</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2262</v>
+        <v>2.4904</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.547</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.109</v>
+        <v>0.7398</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8872</v>
+        <v>3.0113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9961</v>
+        <v>-2.2715</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6805</v>
+        <v>3.3937</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2113</v>
+        <v>-3.9169</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8918</v>
+        <v>7.3106</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7943</v>
+        <v>5.9406</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.227</v>
+        <v>-1.9323</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5673</v>
+        <v>7.8729</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1137</v>
+        <v>-2.5469</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4383</v>
+        <v>-1.9846</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3245</v>
+        <v>-0.5622</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5661</v>
+        <v>2.8305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2234</v>
+        <v>-1.7106</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0929</v>
+        <v>-0.7026</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3163</v>
+        <v>-1.0081</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0156</v>
+        <v>0.2955</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6215</v>
+        <v>-0.5949</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6371</v>
+        <v>0.8903</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3937</v>
+        <v>-0.6805</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.9169</v>
+        <v>0.2113</v>
       </c>
       <c r="I20" t="n">
-        <v>7.3106</v>
+        <v>-0.8918</v>
       </c>
       <c r="J20" t="n">
-        <v>5.9406</v>
+        <v>-0.7943</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9323</v>
+        <v>-0.227</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8729</v>
+        <v>-0.5673</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5469</v>
+        <v>0.1137</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9846</v>
+        <v>0.4383</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5622</v>
+        <v>-0.3245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8305</v>
+        <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.466</v>
+        <v>0.4099</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0923</v>
+        <v>0.1994</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3737</v>
+        <v>0.2105</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8868</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3398</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6315</v>
+        <v>-0.4101</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9917</v>
+        <v>2.1866</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6232</v>
+        <v>-2.5967</v>
       </c>
       <c r="G21" t="n">
         <v>1.8073</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2691</v>
+        <v>-1.0478</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3404</v>
+        <v>-0.1455</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9288</v>
+        <v>-0.9023</v>
       </c>
       <c r="V21" t="n">
         <v>-1.547</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1366</v>
+        <v>-1.1414</v>
       </c>
       <c r="E22" t="n">
         <v>0.2452</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3818</v>
+        <v>-1.3865</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6489</v>
@@ -2170,13 +2170,13 @@
         <v>3.0192</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2991</v>
+        <v>-1.3038</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5603</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7388</v>
+        <v>-0.7435</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3208</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8474</v>
+        <v>-1.4409</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2187</v>
+        <v>0.4135</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.066</v>
+        <v>-1.8544</v>
       </c>
       <c r="G23" t="n">
         <v>0.249</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4737</v>
+        <v>-1.0672</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5755</v>
+        <v>-0.3807</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8982</v>
+        <v>-0.6866</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6226</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6742</v>
+        <v>-4.0951</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0319</v>
+        <v>-0.4217</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6423</v>
+        <v>-3.6734</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3377</v>
@@ -2326,13 +2326,13 @@
         <v>2.4531</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6443</v>
+        <v>0.2234</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5131</v>
+        <v>0.1234</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1312</v>
+        <v>0.1</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4904</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5651</v>
+        <v>-4.4858</v>
       </c>
       <c r="E25" t="n">
         <v>-0.8439</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7212</v>
+        <v>-3.6419</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1647</v>
@@ -2404,13 +2404,13 @@
         <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1693</v>
       </c>
       <c r="T25" t="n">
         <v>0.4979</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.408</v>
+        <v>-0.3286</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8678</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.9349</v>
+        <v>5.234000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>21.145</v>
+        <v>21.1449</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.2101</v>
+        <v>-15.911</v>
       </c>
       <c r="G26" t="n">
         <v>8.880699999999999</v>
@@ -2473,7 +2473,7 @@
         <v>-8.439</v>
       </c>
       <c r="P26" t="n">
-        <v>7.547999999999999</v>
+        <v>7.548</v>
       </c>
       <c r="Q26" t="n">
         <v>-10.3785</v>
@@ -2482,13 +2482,13 @@
         <v>17.9265</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.2487</v>
+        <v>-4.9496</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7294</v>
+        <v>-0.7295</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.5194</v>
+        <v>-4.2203</v>
       </c>
       <c r="V26" t="n">
         <v>-6.245</v>
